--- a/Dataset/jabalpur_combined.xlsx
+++ b/Dataset/jabalpur_combined.xlsx
@@ -471,10 +471,10 @@
         <v>75.41666666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -494,10 +494,10 @@
         <v>85.33333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -517,10 +517,10 @@
         <v>80.08333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -540,10 +540,10 @@
         <v>96.52777777777777</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -563,10 +563,10 @@
         <v>78.20833333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -586,10 +586,10 @@
         <v>94.16666666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>97.125</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -632,10 +632,10 @@
         <v>110.875</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>91</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -678,10 +678,10 @@
         <v>88.83333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -701,10 +701,10 @@
         <v>97.875</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -724,10 +724,10 @@
         <v>104.125</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -747,10 +747,10 @@
         <v>132</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -770,10 +770,10 @@
         <v>114.375</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         <v>100.2083333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -816,10 +816,10 @@
         <v>104.9583333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -839,10 +839,10 @@
         <v>112.1666666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -862,10 +862,10 @@
         <v>150.4583333333333</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -885,10 +885,10 @@
         <v>104.75</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -908,10 +908,10 @@
         <v>89.875</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
         <v>98.5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -954,10 +954,10 @@
         <v>101.9583333333333</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         <v>95.58333333333333</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>102.3333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1023,10 +1023,10 @@
         <v>98.125</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1046,10 +1046,10 @@
         <v>80.04166666666667</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1069,10 +1069,10 @@
         <v>73.75</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1092,10 +1092,10 @@
         <v>78.45833333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1115,10 +1115,10 @@
         <v>78.83333333333333</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1138,10 +1138,10 @@
         <v>88.51388888888887</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1161,10 +1161,10 @@
         <v>93.625</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1184,10 +1184,10 @@
         <v>87.41666666666667</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1207,10 +1207,10 @@
         <v>91.58333333333333</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1230,10 +1230,10 @@
         <v>82.70833333333333</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1253,10 +1253,10 @@
         <v>92.375</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1276,10 +1276,10 @@
         <v>85.29166666666667</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>85.25</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1322,10 +1322,10 @@
         <v>73.29166666666667</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>77.58333333333333</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1368,10 +1368,10 @@
         <v>82.5</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>77</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1414,10 +1414,10 @@
         <v>85.5</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>77.91666666666667</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1460,10 +1460,10 @@
         <v>63.5</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1483,10 +1483,10 @@
         <v>66.04166666666667</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1506,10 +1506,10 @@
         <v>72.33333333333333</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1529,10 +1529,10 @@
         <v>70.25</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1552,10 +1552,10 @@
         <v>72.125</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>82.5</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1598,10 +1598,10 @@
         <v>82.04166666666667</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1621,10 +1621,10 @@
         <v>86</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1644,10 +1644,10 @@
         <v>84.125</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1667,10 +1667,10 @@
         <v>72.125</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1690,10 +1690,10 @@
         <v>68.33333333333333</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1713,10 +1713,10 @@
         <v>61.08333333333334</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1736,10 +1736,10 @@
         <v>56.06944444444445</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -1759,10 +1759,10 @@
         <v>63.91666666666666</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -1782,10 +1782,10 @@
         <v>68.41666666666667</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -1805,10 +1805,10 @@
         <v>59.58333333333334</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -1828,10 +1828,10 @@
         <v>73.5</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -1851,10 +1851,10 @@
         <v>77.875</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -1874,10 +1874,10 @@
         <v>67.25</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -1897,10 +1897,10 @@
         <v>77.08333333333333</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -1920,10 +1920,10 @@
         <v>74.625</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
         <v>65.61111111111111</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -1966,10 +1966,10 @@
         <v>68.54166666666667</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -1989,10 +1989,10 @@
         <v>71.45833333333333</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2012,10 +2012,10 @@
         <v>77.75</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2035,10 +2035,10 @@
         <v>77.58333333333333</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -2058,10 +2058,10 @@
         <v>86.8611111111111</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         <v>92.45833333333333</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -2104,10 +2104,10 @@
         <v>90.16666666666667</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>95.58333333333333</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -2150,10 +2150,10 @@
         <v>70.45833333333333</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -2173,10 +2173,10 @@
         <v>69.70833333333333</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -2196,10 +2196,10 @@
         <v>68</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>83</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -2242,10 +2242,10 @@
         <v>84</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         <v>71.66666666666667</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>67.66666666666667</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         <v>69.70833333333333</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2334,10 +2334,10 @@
         <v>74.70833333333333</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2357,10 +2357,10 @@
         <v>73.52777777777777</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2380,10 +2380,10 @@
         <v>80.125</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2403,10 +2403,10 @@
         <v>81.29166666666667</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2426,10 +2426,10 @@
         <v>92.79166666666667</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>102.5</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>103.9583333333333</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>103.4583333333333</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2518,10 +2518,10 @@
         <v>99.16666666666667</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -2541,10 +2541,10 @@
         <v>114.375</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -2564,10 +2564,10 @@
         <v>116.9583333333333</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -2587,10 +2587,10 @@
         <v>107.4375</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -2610,10 +2610,10 @@
         <v>79.83333333333333</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -2633,10 +2633,10 @@
         <v>100.1666666666667</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -2656,10 +2656,10 @@
         <v>113.0833333333333</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -2679,10 +2679,10 @@
         <v>100.6666666666667</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>93.04166666666667</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -2725,10 +2725,10 @@
         <v>104.875</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>79.83333333333333</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -2771,10 +2771,10 @@
         <v>113.5694444444445</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -2794,10 +2794,10 @@
         <v>101.5833333333333</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -2817,10 +2817,10 @@
         <v>101.0833333333333</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>80.08333333333333</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -2863,10 +2863,10 @@
         <v>84.33333333333333</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -2886,10 +2886,10 @@
         <v>82.95833333333333</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -2909,10 +2909,10 @@
         <v>86.375</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -2932,10 +2932,10 @@
         <v>89.54166666666667</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -2955,10 +2955,10 @@
         <v>88.04166666666667</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -2978,10 +2978,10 @@
         <v>96.16666666666667</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -3001,10 +3001,10 @@
         <v>91.75</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -3024,10 +3024,10 @@
         <v>103.625</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -3047,10 +3047,10 @@
         <v>107.2638888888889</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -3070,10 +3070,10 @@
         <v>104.5416666666667</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -3093,10 +3093,10 @@
         <v>102.4166666666667</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>92.29166666666667</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -3139,10 +3139,10 @@
         <v>85.04166666666667</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -3162,10 +3162,10 @@
         <v>63.625</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -3185,10 +3185,10 @@
         <v>71.45833333333333</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -3208,10 +3208,10 @@
         <v>70.875</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -3231,10 +3231,10 @@
         <v>70.45833333333333</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3254,10 +3254,10 @@
         <v>73.16666666666667</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -3277,10 +3277,10 @@
         <v>76.83333333333333</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -3300,10 +3300,10 @@
         <v>74.375</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -3323,10 +3323,10 @@
         <v>62.83333333333334</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -3346,10 +3346,10 @@
         <v>65.79166666666667</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -3369,10 +3369,10 @@
         <v>64.08333333333333</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -3392,10 +3392,10 @@
         <v>64.54166666666667</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -3415,10 +3415,10 @@
         <v>67.02777777777777</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -3438,10 +3438,10 @@
         <v>73.16666666666667</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>70.79166666666667</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -3484,10 +3484,10 @@
         <v>72.83333333333333</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -3507,10 +3507,10 @@
         <v>73.75</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -3530,10 +3530,10 @@
         <v>77.875</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -3553,10 +3553,10 @@
         <v>78.86111111111111</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -3576,10 +3576,10 @@
         <v>72.66666666666667</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -3599,10 +3599,10 @@
         <v>78.33333333333333</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -3622,10 +3622,10 @@
         <v>82.875</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -3645,10 +3645,10 @@
         <v>81.25</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -3668,10 +3668,10 @@
         <v>75.70833333333333</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -3691,10 +3691,10 @@
         <v>77</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -3714,10 +3714,10 @@
         <v>71.79166666666667</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -3737,10 +3737,10 @@
         <v>64.875</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -3760,10 +3760,10 @@
         <v>57.84722222222222</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -3783,10 +3783,10 @@
         <v>68.125</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -3806,10 +3806,10 @@
         <v>72.72222222222221</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -3829,10 +3829,10 @@
         <v>70</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -3852,10 +3852,10 @@
         <v>80</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -3875,10 +3875,10 @@
         <v>72.875</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>83.66666666666667</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -3921,10 +3921,10 @@
         <v>83</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>106.125</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -3967,10 +3967,10 @@
         <v>92.375</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -3990,10 +3990,10 @@
         <v>70.70833333333333</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -4013,10 +4013,10 @@
         <v>82.33333333333333</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>84.0138888888889</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -4059,10 +4059,10 @@
         <v>110.25</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -4082,10 +4082,10 @@
         <v>127.0833333333333</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -4105,10 +4105,10 @@
         <v>115.1527777777778</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -4128,10 +4128,10 @@
         <v>139.0416666666667</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -4151,10 +4151,10 @@
         <v>146.4166666666667</v>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>108.375</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -4197,10 +4197,10 @@
         <v>87.875</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -4220,10 +4220,10 @@
         <v>85.04166666666667</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -4243,10 +4243,10 @@
         <v>62.25</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -4266,10 +4266,10 @@
         <v>58.41666666666666</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -4289,10 +4289,10 @@
         <v>52.04166666666666</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -4312,10 +4312,10 @@
         <v>54</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -4335,10 +4335,10 @@
         <v>70.875</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -4358,10 +4358,10 @@
         <v>58.83333333333334</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
@@ -4381,10 +4381,10 @@
         <v>44.08333333333334</v>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -4404,10 +4404,10 @@
         <v>67.5</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>67.08333333333333</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -4450,10 +4450,10 @@
         <v>51.5</v>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>45.08333333333334</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
@@ -4496,10 +4496,10 @@
         <v>59.66666666666666</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -4519,10 +4519,10 @@
         <v>62.19444444444445</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
@@ -4542,10 +4542,10 @@
         <v>58</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
@@ -4565,10 +4565,10 @@
         <v>47</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" t="n">
         <v>0</v>
@@ -4588,10 +4588,10 @@
         <v>50.45833333333334</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
@@ -4611,10 +4611,10 @@
         <v>42.54166666666666</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -4634,10 +4634,10 @@
         <v>44.17391304347826</v>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
@@ -4657,10 +4657,10 @@
         <v>42.45833333333334</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
@@ -4680,10 +4680,10 @@
         <v>48.375</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
@@ -4703,10 +4703,10 @@
         <v>45.95833333333334</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -4726,10 +4726,10 @@
         <v>51.25</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>44.5</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
@@ -4772,10 +4772,10 @@
         <v>41.70833333333334</v>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -4795,10 +4795,10 @@
         <v>35.20833333333334</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
@@ -4818,10 +4818,10 @@
         <v>38.79166666666666</v>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -4841,10 +4841,10 @@
         <v>43.58333333333334</v>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -4864,10 +4864,10 @@
         <v>44.08333333333334</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -4887,10 +4887,10 @@
         <v>41.29166666666666</v>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
@@ -4910,10 +4910,10 @@
         <v>41.29166666666666</v>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
@@ -4933,10 +4933,10 @@
         <v>42.79166666666666</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
@@ -4956,10 +4956,10 @@
         <v>43.16666666666666</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -4979,10 +4979,10 @@
         <v>42.95833333333334</v>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -5002,10 +5002,10 @@
         <v>49.375</v>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
@@ -5025,10 +5025,10 @@
         <v>44.625</v>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
@@ -5048,10 +5048,10 @@
         <v>58.70833333333334</v>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" t="n">
         <v>0</v>
@@ -5071,10 +5071,10 @@
         <v>86.16666666666667</v>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>78.54166666666667</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -5117,10 +5117,10 @@
         <v>46.45833333333334</v>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F204" t="n">
         <v>0</v>
@@ -5140,10 +5140,10 @@
         <v>45.09722222222222</v>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
@@ -5163,10 +5163,10 @@
         <v>44.70833333333334</v>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F206" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>41</v>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F207" t="n">
         <v>0</v>
@@ -5209,10 +5209,10 @@
         <v>40.625</v>
       </c>
       <c r="D208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>42.34722222222222</v>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
@@ -5255,10 +5255,10 @@
         <v>33.875</v>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -5278,10 +5278,10 @@
         <v>43.95833333333334</v>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
@@ -5301,10 +5301,10 @@
         <v>42.70833333333334</v>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
@@ -5324,10 +5324,10 @@
         <v>46.66666666666666</v>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F213" t="n">
         <v>0</v>
@@ -5347,10 +5347,10 @@
         <v>61.45833333333334</v>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F214" t="n">
         <v>0</v>
@@ -5370,10 +5370,10 @@
         <v>55.08333333333334</v>
       </c>
       <c r="D215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
@@ -5393,10 +5393,10 @@
         <v>51.79166666666666</v>
       </c>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
@@ -5416,10 +5416,10 @@
         <v>66.625</v>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
@@ -5439,10 +5439,10 @@
         <v>59.54166666666666</v>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -5462,10 +5462,10 @@
         <v>64.75</v>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
@@ -5485,10 +5485,10 @@
         <v>77.73611111111111</v>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
@@ -5508,10 +5508,10 @@
         <v>60.79166666666666</v>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
@@ -5531,10 +5531,10 @@
         <v>50.91666666666666</v>
       </c>
       <c r="D222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
@@ -5554,10 +5554,10 @@
         <v>51.04166666666666</v>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F223" t="n">
         <v>0</v>
@@ -5577,10 +5577,10 @@
         <v>42.70833333333334</v>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
@@ -5600,10 +5600,10 @@
         <v>42.75</v>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
@@ -5623,10 +5623,10 @@
         <v>52.75</v>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F226" t="n">
         <v>0</v>
@@ -5646,10 +5646,10 @@
         <v>53.5</v>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -5669,10 +5669,10 @@
         <v>50.70833333333334</v>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
@@ -5692,10 +5692,10 @@
         <v>57.29166666666666</v>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F229" t="n">
         <v>0</v>
@@ -5715,10 +5715,10 @@
         <v>59.16666666666666</v>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F230" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>47.66666666666666</v>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
@@ -5761,10 +5761,10 @@
         <v>45.5</v>
       </c>
       <c r="D232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
@@ -5784,10 +5784,10 @@
         <v>47.08333333333334</v>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
         <v>0</v>
@@ -5807,10 +5807,10 @@
         <v>41.08333333333334</v>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
@@ -5830,10 +5830,10 @@
         <v>37.08333333333334</v>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -5853,10 +5853,10 @@
         <v>36.16666666666666</v>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -5876,10 +5876,10 @@
         <v>44.29166666666666</v>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
@@ -5899,10 +5899,10 @@
         <v>54.625</v>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -5922,10 +5922,10 @@
         <v>54.33333333333334</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -5945,10 +5945,10 @@
         <v>61.58333333333334</v>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>55.04166666666668</v>
       </c>
       <c r="D241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F241" t="n">
         <v>0</v>
@@ -5991,10 +5991,10 @@
         <v>45.33333333333334</v>
       </c>
       <c r="D242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F242" t="n">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         <v>51.625</v>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F243" t="n">
         <v>0</v>
@@ -6037,10 +6037,10 @@
         <v>48.91666666666666</v>
       </c>
       <c r="D244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
@@ -6060,10 +6060,10 @@
         <v>38.38095238095238</v>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F245" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>31.54166666666667</v>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
@@ -6106,10 +6106,10 @@
         <v>38.125</v>
       </c>
       <c r="D247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
@@ -6129,10 +6129,10 @@
         <v>42.01388888888889</v>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F248" t="n">
         <v>0</v>
@@ -6152,10 +6152,10 @@
         <v>36.98611111111111</v>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F249" t="n">
         <v>0</v>
@@ -6175,10 +6175,10 @@
         <v>38.63888888888889</v>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F250" t="n">
         <v>0</v>
@@ -6198,10 +6198,10 @@
         <v>39.41666666666666</v>
       </c>
       <c r="D251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F251" t="n">
         <v>0</v>
@@ -6221,10 +6221,10 @@
         <v>35.81944444444444</v>
       </c>
       <c r="D252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F252" t="n">
         <v>0</v>
@@ -6244,10 +6244,10 @@
         <v>35.04166666666666</v>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F253" t="n">
         <v>0</v>
@@ -6267,10 +6267,10 @@
         <v>46.25</v>
       </c>
       <c r="D254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F254" t="n">
         <v>0</v>
@@ -6290,10 +6290,10 @@
         <v>56.75</v>
       </c>
       <c r="D255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -6313,10 +6313,10 @@
         <v>43.875</v>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F256" t="n">
         <v>0</v>
@@ -6336,10 +6336,10 @@
         <v>48.375</v>
       </c>
       <c r="D257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F257" t="n">
         <v>0</v>
@@ -6359,10 +6359,10 @@
         <v>60.40277777777777</v>
       </c>
       <c r="D258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F258" t="n">
         <v>0</v>
@@ -6382,10 +6382,10 @@
         <v>72.70833333333333</v>
       </c>
       <c r="D259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
@@ -6405,10 +6405,10 @@
         <v>49.29166666666666</v>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
@@ -6428,10 +6428,10 @@
         <v>48.66666666666666</v>
       </c>
       <c r="D261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
@@ -6451,10 +6451,10 @@
         <v>47.33333333333334</v>
       </c>
       <c r="D262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F262" t="n">
         <v>0</v>
@@ -6474,10 +6474,10 @@
         <v>63.16666666666666</v>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
@@ -6497,10 +6497,10 @@
         <v>57.08333333333334</v>
       </c>
       <c r="D264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
@@ -6520,10 +6520,10 @@
         <v>55.75</v>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F265" t="n">
         <v>0</v>
@@ -6543,10 +6543,10 @@
         <v>66.54166666666667</v>
       </c>
       <c r="D266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F266" t="n">
         <v>0</v>
@@ -6566,10 +6566,10 @@
         <v>72.66666666666667</v>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F267" t="n">
         <v>0</v>
@@ -6589,10 +6589,10 @@
         <v>69.95833333333333</v>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F268" t="n">
         <v>0</v>
@@ -6612,10 +6612,10 @@
         <v>77.91666666666667</v>
       </c>
       <c r="D269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F269" t="n">
         <v>0</v>
@@ -6635,10 +6635,10 @@
         <v>59.25</v>
       </c>
       <c r="D270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F270" t="n">
         <v>0</v>
@@ -6658,10 +6658,10 @@
         <v>41</v>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F271" t="n">
         <v>0</v>
@@ -6681,10 +6681,10 @@
         <v>43</v>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F272" t="n">
         <v>0</v>
@@ -6704,10 +6704,10 @@
         <v>48.25</v>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F273" t="n">
         <v>0</v>
@@ -6727,10 +6727,10 @@
         <v>46.875</v>
       </c>
       <c r="D274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F274" t="n">
         <v>0</v>
@@ -6750,10 +6750,10 @@
         <v>51.45833333333334</v>
       </c>
       <c r="D275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F275" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>44.04166666666666</v>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F276" t="n">
         <v>0</v>
@@ -6796,10 +6796,10 @@
         <v>52.33333333333334</v>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F277" t="n">
         <v>0</v>
@@ -6819,10 +6819,10 @@
         <v>45.54166666666666</v>
       </c>
       <c r="D278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F278" t="n">
         <v>0</v>
@@ -6842,10 +6842,10 @@
         <v>42.95833333333334</v>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
@@ -6865,10 +6865,10 @@
         <v>49</v>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F280" t="n">
         <v>0</v>
@@ -6888,10 +6888,10 @@
         <v>61.58333333333334</v>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F281" t="n">
         <v>0</v>
@@ -6911,10 +6911,10 @@
         <v>63.54166666666666</v>
       </c>
       <c r="D282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F282" t="n">
         <v>0</v>
@@ -6934,10 +6934,10 @@
         <v>67.11111111111111</v>
       </c>
       <c r="D283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F283" t="n">
         <v>0</v>
@@ -6957,10 +6957,10 @@
         <v>111.4166666666667</v>
       </c>
       <c r="D284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F284" t="n">
         <v>0</v>
@@ -6980,10 +6980,10 @@
         <v>130.25</v>
       </c>
       <c r="D285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F285" t="n">
         <v>0</v>
@@ -7003,10 +7003,10 @@
         <v>97.11111111111113</v>
       </c>
       <c r="D286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
@@ -7026,10 +7026,10 @@
         <v>88.5</v>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F287" t="n">
         <v>0</v>
@@ -7049,10 +7049,10 @@
         <v>98.125</v>
       </c>
       <c r="D288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
@@ -7072,10 +7072,10 @@
         <v>121.3611111111111</v>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
@@ -7095,10 +7095,10 @@
         <v>113.5972222222222</v>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F290" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>111.4166666666667</v>
       </c>
       <c r="D291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F291" t="n">
         <v>0</v>
@@ -7141,10 +7141,10 @@
         <v>98.91666666666667</v>
       </c>
       <c r="D292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F292" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>91.95833333333333</v>
       </c>
       <c r="D293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F293" t="n">
         <v>0</v>
@@ -7187,10 +7187,10 @@
         <v>112.9583333333333</v>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
@@ -7210,10 +7210,10 @@
         <v>186.0416666666667</v>
       </c>
       <c r="D295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F295" t="n">
         <v>0</v>
@@ -7233,10 +7233,10 @@
         <v>139.5972222222222</v>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F296" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>81.81944444444444</v>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F297" t="n">
         <v>0</v>
@@ -7279,10 +7279,10 @@
         <v>139.9166666666667</v>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F298" t="n">
         <v>0</v>
@@ -7302,10 +7302,10 @@
         <v>163.9166666666667</v>
       </c>
       <c r="D299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F299" t="n">
         <v>0</v>
@@ -7325,10 +7325,10 @@
         <v>150.9583333333333</v>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F300" t="n">
         <v>0</v>
@@ -7348,10 +7348,10 @@
         <v>55.75</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F301" t="n">
         <v>0</v>
@@ -7371,10 +7371,10 @@
         <v>82.125</v>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F302" t="n">
         <v>0</v>
@@ -7394,10 +7394,10 @@
         <v>95.16666666666667</v>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F303" t="n">
         <v>0</v>
@@ -7417,10 +7417,10 @@
         <v>71.83333333333333</v>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F304" t="n">
         <v>0</v>
@@ -7440,10 +7440,10 @@
         <v>53.20833333333334</v>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F305" t="n">
         <v>0</v>
@@ -7463,10 +7463,10 @@
         <v>53.83333333333334</v>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F306" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>94.91666666666667</v>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F307" t="n">
         <v>0</v>
@@ -7509,10 +7509,10 @@
         <v>105.375</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F308" t="n">
         <v>0</v>
@@ -7532,10 +7532,10 @@
         <v>105.1666666666667</v>
       </c>
       <c r="D309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F309" t="n">
         <v>0</v>
@@ -7555,10 +7555,10 @@
         <v>113.0833333333333</v>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F310" t="n">
         <v>0</v>
@@ -7578,10 +7578,10 @@
         <v>112.8333333333333</v>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F311" t="n">
         <v>0</v>
@@ -7601,10 +7601,10 @@
         <v>106.3333333333333</v>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F312" t="n">
         <v>0</v>
@@ -7624,10 +7624,10 @@
         <v>133.4722222222222</v>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F313" t="n">
         <v>0</v>
@@ -7647,10 +7647,10 @@
         <v>151.5833333333333</v>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
@@ -7670,10 +7670,10 @@
         <v>162.9583333333333</v>
       </c>
       <c r="D315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F315" t="n">
         <v>0</v>
@@ -7693,10 +7693,10 @@
         <v>161.375</v>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F316" t="n">
         <v>0</v>
@@ -7716,10 +7716,10 @@
         <v>174.3333333333333</v>
       </c>
       <c r="D317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
@@ -7739,10 +7739,10 @@
         <v>193.8333333333333</v>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F318" t="n">
         <v>0</v>
@@ -7762,10 +7762,10 @@
         <v>175.0833333333333</v>
       </c>
       <c r="D319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F319" t="n">
         <v>0</v>
@@ -7785,10 +7785,10 @@
         <v>162.4166666666667</v>
       </c>
       <c r="D320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F320" t="n">
         <v>0</v>
@@ -7808,10 +7808,10 @@
         <v>175.5416666666667</v>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F321" t="n">
         <v>0</v>
@@ -7831,10 +7831,10 @@
         <v>224.4166666666667</v>
       </c>
       <c r="D322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F322" t="n">
         <v>0</v>
@@ -7854,10 +7854,10 @@
         <v>183.375</v>
       </c>
       <c r="D323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F323" t="n">
         <v>0</v>
@@ -7877,10 +7877,10 @@
         <v>201.1666666666667</v>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F324" t="n">
         <v>0</v>
@@ -7900,10 +7900,10 @@
         <v>221.2222222222222</v>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F325" t="n">
         <v>0</v>
@@ -7923,10 +7923,10 @@
         <v>222</v>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F326" t="n">
         <v>0</v>
@@ -7946,10 +7946,10 @@
         <v>212.7083333333333</v>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F327" t="n">
         <v>0</v>
@@ -7969,10 +7969,10 @@
         <v>177.375</v>
       </c>
       <c r="D328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F328" t="n">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>163.375</v>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F329" t="n">
         <v>0</v>
@@ -8015,10 +8015,10 @@
         <v>139.875</v>
       </c>
       <c r="D330" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F330" t="n">
         <v>0</v>
@@ -8038,10 +8038,10 @@
         <v>141.375</v>
       </c>
       <c r="D331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F331" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>100.8888888888889</v>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F332" t="n">
         <v>0</v>
@@ -8084,10 +8084,10 @@
         <v>117.0833333333333</v>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F333" t="n">
         <v>0</v>
@@ -8107,10 +8107,10 @@
         <v>150.625</v>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F334" t="n">
         <v>0</v>
@@ -8130,10 +8130,10 @@
         <v>147.2083333333333</v>
       </c>
       <c r="D335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
@@ -8153,10 +8153,10 @@
         <v>117.1666666666667</v>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
@@ -8176,10 +8176,10 @@
         <v>105.1666666666667</v>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F337" t="n">
         <v>0</v>
@@ -8199,10 +8199,10 @@
         <v>99.54166666666667</v>
       </c>
       <c r="D338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F338" t="n">
         <v>0</v>
@@ -8222,10 +8222,10 @@
         <v>84.125</v>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F339" t="n">
         <v>0</v>
@@ -8245,10 +8245,10 @@
         <v>107.2916666666667</v>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F340" t="n">
         <v>0</v>
@@ -8268,10 +8268,10 @@
         <v>107.3333333333333</v>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F341" t="n">
         <v>0</v>
@@ -8291,10 +8291,10 @@
         <v>130.0416666666667</v>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
@@ -8314,10 +8314,10 @@
         <v>121</v>
       </c>
       <c r="D343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F343" t="n">
         <v>0</v>
@@ -8337,10 +8337,10 @@
         <v>91.25</v>
       </c>
       <c r="D344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F344" t="n">
         <v>0</v>
@@ -8360,10 +8360,10 @@
         <v>96.5</v>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F345" t="n">
         <v>0</v>
@@ -8383,10 +8383,10 @@
         <v>112.7777777777778</v>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F346" t="n">
         <v>0</v>
@@ -8406,10 +8406,10 @@
         <v>101.4583333333333</v>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F347" t="n">
         <v>0</v>
@@ -8429,10 +8429,10 @@
         <v>104.5</v>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F348" t="n">
         <v>0</v>
@@ -8452,10 +8452,10 @@
         <v>125.0416666666667</v>
       </c>
       <c r="D349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F349" t="n">
         <v>0</v>
@@ -8475,10 +8475,10 @@
         <v>193.5416666666667</v>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>205.7083333333333</v>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F351" t="n">
         <v>0</v>
@@ -8521,10 +8521,10 @@
         <v>120.7916666666667</v>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F352" t="n">
         <v>0</v>
@@ -8544,10 +8544,10 @@
         <v>83.16666666666667</v>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F353" t="n">
         <v>0</v>
@@ -8567,10 +8567,10 @@
         <v>80.5</v>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F354" t="n">
         <v>0</v>
@@ -8590,10 +8590,10 @@
         <v>102.8333333333333</v>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F355" t="n">
         <v>0</v>
@@ -8613,10 +8613,10 @@
         <v>92.54166666666667</v>
       </c>
       <c r="D356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F356" t="n">
         <v>0</v>
@@ -8636,10 +8636,10 @@
         <v>90.83333333333333</v>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F357" t="n">
         <v>0</v>
@@ -8659,10 +8659,10 @@
         <v>129.6666666666667</v>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F358" t="n">
         <v>0</v>
@@ -8682,10 +8682,10 @@
         <v>85.41666666666667</v>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F359" t="n">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>83.125</v>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F360" t="n">
         <v>0</v>
@@ -8728,10 +8728,10 @@
         <v>77.20833333333333</v>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F361" t="n">
         <v>0</v>
@@ -8751,10 +8751,10 @@
         <v>74</v>
       </c>
       <c r="D362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F362" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>82.25</v>
       </c>
       <c r="D363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F363" t="n">
         <v>0</v>
@@ -8797,10 +8797,10 @@
         <v>93.66666666666667</v>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
@@ -8820,10 +8820,10 @@
         <v>76.625</v>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F365" t="n">
         <v>0</v>
@@ -8843,10 +8843,10 @@
         <v>73</v>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F366" t="n">
         <v>0</v>
